--- a/mixs-templates/MigsEu_plus_combinations/MigsEuHostAssociated.xlsx
+++ b/mixs-templates/MigsEu_plus_combinations/MigsEuHostAssociated.xlsx
@@ -479,7 +479,7 @@
       </c>
       <c r="M1" t="inlineStr">
         <is>
-          <t>estimated_size</t>
+          <t>estimated_genome_size</t>
         </is>
       </c>
       <c r="N1" t="inlineStr">
